--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5377,6 +5377,126 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122394474</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98175</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Berg, Berg, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>584257</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6538303</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lerbo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5379,10 +5379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122394474</v>
+        <v>122394476</v>
       </c>
       <c r="B38" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5379,7 +5379,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122394476</v>
+        <v>122394474</v>
       </c>
       <c r="B38" t="n">
         <v>98185</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>122394474</v>
       </c>
       <c r="B38" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>122394474</v>
       </c>
       <c r="B38" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>122394474</v>
       </c>
       <c r="B38" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5396,11 +5396,6 @@
       </c>
       <c r="E38" t="n">
         <v>220787</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5379,10 +5379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122394474</v>
+        <v>122394476</v>
       </c>
       <c r="B38" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5397,6 +5397,11 @@
       <c r="E38" t="n">
         <v>220787</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -5409,7 +5414,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5457,7 +5462,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5467,7 +5472,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5379,10 +5379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122394476</v>
+        <v>122394474</v>
       </c>
       <c r="B38" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5379,7 +5379,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122394474</v>
+        <v>122394476</v>
       </c>
       <c r="B38" t="n">
         <v>98237</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -5382,7 +5382,7 @@
         <v>122394476</v>
       </c>
       <c r="B38" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98156145</v>
+        <v>106563118</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lerbo Berg 2, Srm</t>
+          <t>Berg Lerbo, blåmossa 360 m s, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584386.4101965474</v>
+        <v>584293</v>
       </c>
       <c r="R2" t="n">
-        <v>6538141.304018256</v>
+        <v>6538264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Två lokaler med 9 meters mellanrum, med 6 respektive ca 85 bladrosetter.</t>
+          <t>på flera ställen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,80 +767,77 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98158007</v>
+        <v>106563513</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lerbo Berg 7, Srm</t>
+          <t>Berg Lerbo, motaggsvamp 370 m s, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584339.5836724243</v>
+        <v>584277</v>
       </c>
       <c r="R3" t="n">
-        <v>6538085.608313028</v>
+        <v>6538272</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,27 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fyra lokaler med 11 + 2 + 20 + 2 bladrosetter, 4-9 meter mellan lokalerna.</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,77 +879,74 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98158382</v>
+        <v>106563582</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lerbo Berg 8, Srm</t>
+          <t>Berga Lerbo, motaggsvamp 400 m s, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584322.5081399854</v>
+        <v>584335</v>
       </c>
       <c r="R4" t="n">
-        <v>6538086.780837334</v>
+        <v>6538211</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,22 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,80 +991,84 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98157785</v>
+        <v>106692476</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4189</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lerbo Berg 6, Srm</t>
+          <t>Berg, S om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584349.2217702151</v>
+        <v>584353</v>
       </c>
       <c r="R5" t="n">
-        <v>6538117.279694059</v>
+        <v>6538074</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,27 +1092,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två lokaler med 5-9 meters mellanrum. Med 5 och 11 bladrosetter.</t>
+          <t>Ett fjolårsex under gammal gran. Området är avverkningsanmält.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,81 +1111,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98155950</v>
+        <v>106563215</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lerbo Berg NV 1, Srm</t>
+          <t>Berg Lerbo, blåmossa 360 m s, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584257.0846869629</v>
+        <v>584293</v>
       </c>
       <c r="R6" t="n">
-        <v>6538290.088085855</v>
+        <v>6538264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,27 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tre smålokaler med 3-4 meters mellanrum. Med 5, 10 och 16 bladrosetter.</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,80 +1215,76 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98156284</v>
+        <v>106563756</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lerbo Berg 4, Srm</t>
+          <t>Berg Lerbo, dropptaggsvamp 415 m s, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584370.8007180344</v>
+        <v>584321</v>
       </c>
       <c r="R7" t="n">
-        <v>6538169.842088223</v>
+        <v>6538094</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1402,27 +1308,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>En lokal på några kvadratmeter med 12 rosetter.</t>
+          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,52 +1331,57 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98158635</v>
+        <v>106562883</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1490,25 +1391,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lerbo berg 10, Srm</t>
+          <t>Berg Lerbo, 320 m s, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584348.230930091</v>
+        <v>584231</v>
       </c>
       <c r="R8" t="n">
-        <v>6538068.262973726</v>
+        <v>6538308</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1532,27 +1432,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 10 meter NV om parkeringsficka.</t>
+          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,77 +1455,73 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98156204</v>
+        <v>106563629</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lerbo Berg 3, Srm</t>
+          <t>Berg Lerbo, grovticka 425 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584366.5604923052</v>
+        <v>584354</v>
       </c>
       <c r="R9" t="n">
-        <v>6538151.182805483</v>
+        <v>6538171</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1662,27 +1548,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Tre lokaler med 9 meter mellan, med 6, 7 och 10 bladrosetter.</t>
+          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,80 +1571,84 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98158490</v>
+        <v>106563772</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lerbo Berg 11, Srm</t>
+          <t>Berg Lerbo, dropptaggsvamp 415 m s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584233.0033394973</v>
+        <v>584321</v>
       </c>
       <c r="R10" t="n">
-        <v>6538304.515716649</v>
+        <v>6538094</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1792,22 +1672,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,80 +1695,83 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98158571</v>
+        <v>99035434</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lerbo Berg 12, Srm</t>
+          <t>Katrineholm, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584230.5151383405</v>
+        <v>584260</v>
       </c>
       <c r="R11" t="n">
-        <v>6538276.612874148</v>
+        <v>6538254</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1917,27 +1795,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tre lokaler med 4-9 meters mellanrum. Med 38, 12 och 5 bladrosetter.</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1946,34 +1819,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monika Gustafsson</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99035434</v>
+        <v>106563508</v>
       </c>
       <c r="B12" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,26 +1848,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2009,19 +1876,20 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Katrineholm, Srm</t>
+          <t>Berg Lerbo, motaggsvamp 370 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584259.9526648163</v>
+        <v>584277</v>
       </c>
       <c r="R12" t="n">
-        <v>6538253.535413696</v>
+        <v>6538272</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2045,22 +1913,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:54</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:54</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2069,82 +1932,88 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99035745</v>
+        <v>106563577</v>
       </c>
       <c r="B13" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sund Katrineborg, Katrineholm, Srm</t>
+          <t>Berga Lerbo, motaggsvamp 400 m s, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584329.8318954482</v>
+        <v>584335</v>
       </c>
       <c r="R13" t="n">
-        <v>6538129.747484392</v>
+        <v>6538211</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2168,22 +2037,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,82 +2056,88 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99035198</v>
+        <v>106563712</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Katrineholm, Srm</t>
+          <t>Berg Lerbo motaggsvamp 400 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584259.9526648163</v>
+        <v>584292</v>
       </c>
       <c r="R14" t="n">
-        <v>6538253.535413696</v>
+        <v>6538140</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2291,22 +2161,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2315,82 +2180,88 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99110942</v>
+        <v>106563983</v>
       </c>
       <c r="B15" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sund Katrineborg, Katrineholm, Srm</t>
+          <t>Berg Lerbo, motaggsvamp 430 m s, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584359.6743956967</v>
+        <v>584310</v>
       </c>
       <c r="R15" t="n">
-        <v>6538111.83605085</v>
+        <v>6538075</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2414,22 +2285,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>fjolårsex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2438,84 +2304,80 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Dan Åman</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106563242</v>
+        <v>106627332</v>
       </c>
       <c r="B16" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Berg Lerbo granbarkgnagare 350 m s, Srm</t>
+          <t>Berg, Lerbo, Biesta, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584253.8768374666</v>
+        <v>584321</v>
       </c>
       <c r="R16" t="n">
-        <v>6538271.452165138</v>
+        <v>6538115</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2539,128 +2401,81 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>i några granar</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Daniel Franzén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106563795</v>
+        <v>106692515</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Berg Lerbo, dropptaggsvamp 415 m s, Srm</t>
+          <t>Berg, S om, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584321.3056650457</v>
+        <v>584400</v>
       </c>
       <c r="R17" t="n">
-        <v>6538094.490504271</v>
+        <v>6538083</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2690,65 +2505,39 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106564025</v>
+        <v>106563242</v>
       </c>
       <c r="B18" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2756,39 +2545,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2796,14 +2578,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Berg Lerbo 420 m s, Srm</t>
+          <t>Berg Lerbo granbarkgnagare 350 m s, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584356.8886847812</v>
+        <v>584254</v>
       </c>
       <c r="R18" t="n">
-        <v>6538121.058106194</v>
+        <v>6538272</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2833,19 +2615,14 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>i några granar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,64 +2660,59 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106563712</v>
+        <v>17147551</v>
       </c>
       <c r="B19" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Berg Lerbo motaggsvamp 400 m s, Srm</t>
+          <t>Lerbo Berg 7, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584291.3690984178</v>
+        <v>584340</v>
       </c>
       <c r="R19" t="n">
-        <v>6538140.249761487</v>
+        <v>6538086</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2964,27 +2736,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-02-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>fjolårsex</t>
+          <t>2015-02-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2993,93 +2750,78 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106563772</v>
+        <v>98155950</v>
       </c>
       <c r="B20" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Berg Lerbo, dropptaggsvamp 415 m s, Srm</t>
+          <t>Lerbo Berg NV 1, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584321.3056650457</v>
+        <v>584257</v>
       </c>
       <c r="R20" t="n">
-        <v>6538094.490504271</v>
+        <v>6538290</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3103,27 +2845,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>fjolårsex</t>
+          <t>Tre smålokaler med 3-4 meters mellanrum. Med 5, 10 och 16 bladrosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3136,78 +2868,72 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106563629</v>
+        <v>98156145</v>
       </c>
       <c r="B21" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Berg Lerbo, grovticka 425 m s, Srm</t>
+          <t>Lerbo Berg 2, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584354.2419458929</v>
+        <v>584386</v>
       </c>
       <c r="R21" t="n">
-        <v>6538171.025772231</v>
+        <v>6538141</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3234,27 +2960,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>fjolårsex</t>
+          <t>Två lokaler med 9 meters mellanrum, med 6 respektive ca 85 bladrosetter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3267,78 +2983,72 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106563215</v>
+        <v>98156204</v>
       </c>
       <c r="B22" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Berg Lerbo, blåmossa 360 m s, Srm</t>
+          <t>Lerbo Berg 3, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584292.786769349</v>
+        <v>584367</v>
       </c>
       <c r="R22" t="n">
-        <v>6538264.054031932</v>
+        <v>6538151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3365,22 +3075,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tre lokaler med 9 meter mellan, med 6, 7 och 10 bladrosetter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3393,89 +3098,75 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106563508</v>
+        <v>98156284</v>
       </c>
       <c r="B23" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Berg Lerbo, motaggsvamp 370 m s, Srm</t>
+          <t>Lerbo Berg 4, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584277.1142557467</v>
+        <v>584371</v>
       </c>
       <c r="R23" t="n">
-        <v>6538271.961699993</v>
+        <v>6538170</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3499,27 +3190,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>fjolårsex</t>
+          <t>En lokal på några kvadratmeter med 12 rosetter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3532,81 +3213,75 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106563756</v>
+        <v>98157785</v>
       </c>
       <c r="B24" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Berg Lerbo, dropptaggsvamp 415 m s, Srm</t>
+          <t>Lerbo Berg 6, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584321.3056650457</v>
+        <v>584349</v>
       </c>
       <c r="R24" t="n">
-        <v>6538094.490504271</v>
+        <v>6538117</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3630,27 +3305,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>fjolårsex</t>
+          <t>Två lokaler med 5-9 meters mellanrum. Med 5 och 11 bladrosetter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3663,82 +3328,75 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106563513</v>
+        <v>98158382</v>
       </c>
       <c r="B25" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Berg Lerbo, motaggsvamp 370 m s, Srm</t>
+          <t>Lerbo Berg 8, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584277.1142557467</v>
+        <v>584323</v>
       </c>
       <c r="R25" t="n">
-        <v>6538271.961699993</v>
+        <v>6538087</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3762,22 +3420,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3790,89 +3438,75 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106563983</v>
+        <v>98158490</v>
       </c>
       <c r="B26" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Berg Lerbo, motaggsvamp 430 m s, Srm</t>
+          <t>Lerbo Berg 11, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584310.3630403695</v>
+        <v>584233</v>
       </c>
       <c r="R26" t="n">
-        <v>6538075.168150426</v>
+        <v>6538305</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3896,27 +3530,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>fjolårsex</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3929,79 +3548,72 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106563118</v>
+        <v>98158571</v>
       </c>
       <c r="B27" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Berg Lerbo, blåmossa 360 m s, Srm</t>
+          <t>Lerbo Berg 12, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584292.786769349</v>
+        <v>584231</v>
       </c>
       <c r="R27" t="n">
-        <v>6538264.054031932</v>
+        <v>6538277</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4028,27 +3640,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på flera ställen</t>
+          <t>Tre lokaler med 4-9 meters mellanrum. Med 38, 12 och 5 bladrosetter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4061,62 +3663,47 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>106562883</v>
+        <v>98158635</v>
       </c>
       <c r="B28" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4126,24 +3713,25 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Berg Lerbo, 320 m s, Srm</t>
+          <t>Lerbo berg 10, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584230.342339717</v>
+        <v>584348</v>
       </c>
       <c r="R28" t="n">
-        <v>6538308.067341365</v>
+        <v>6538068</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4167,27 +3755,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>fjolårsex</t>
+          <t>Ca 10 meter NV om parkeringsficka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4200,40 +3778,25 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Monika Gustafsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Monika Gustafsson, Karl-Joel Sundholm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>106627405</v>
+        <v>99035198</v>
       </c>
       <c r="B29" t="n">
-        <v>95529</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4241,38 +3804,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221940</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mellanlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium zeilleri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Berg, Lerbo, Biesta, Srm</t>
+          <t>Katrineholm, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584320.8419535003</v>
+        <v>584260</v>
       </c>
       <c r="R29" t="n">
-        <v>6538115.625454261</v>
+        <v>6538254</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4299,22 +3869,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4323,34 +3893,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>106627978</v>
+        <v>106563795</v>
       </c>
       <c r="B30" t="n">
-        <v>95529</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4358,26 +3922,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221940</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mellanlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium zeilleri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4391,20 +3955,24 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerbo Berg, 400 m SSO om, Srm</t>
+          <t>Berg Lerbo, dropptaggsvamp 415 m s, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584313.495338978</v>
+        <v>584321</v>
       </c>
       <c r="R30" t="n">
-        <v>6538144.34522896</v>
+        <v>6538094</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4428,27 +3996,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Varav två skott tagna som belägg av Bo Karlsson. Tio skott med sporaxskaft med 3-6 sporax per skaft. Sporaxskaften utgår både från centralskottet och från sidogrenar. Smala ändgrenar, cirka 1,5 mm. Dorsalbladen nästan lika stora som lateralbladen i grenspetsarna, ventralbladen något kortare och smalare. Lateralbladens spetsar inböjda, med några få undantag. Jordskott 6-8 cm under yttre markskiktet. Hela beståndet inom ett begränsat område, som i övrigt endast hyser ett fåtal kärlväxter. Skogspartiet är anmält för avverkning.</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4461,20 +4014,25 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Mossig barrblandskog.</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rolf Wahlström, Bo Karlsson</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4484,12 +4042,7 @@
         <v>106627216</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4525,10 +4078,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584320.8419535003</v>
+        <v>584321</v>
       </c>
       <c r="R31" t="n">
-        <v>6538115.625454261</v>
+        <v>6538115</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4558,19 +4111,9 @@
           <t>2023-02-11</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-02-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4603,56 +4146,68 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>106627332</v>
+        <v>106642991</v>
       </c>
       <c r="B32" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Berg, Lerbo, Biesta, Srm</t>
+          <t>Berg Lerbo, knärot 350 m sso, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584320.8419535003</v>
+        <v>584232</v>
       </c>
       <c r="R32" t="n">
-        <v>6538115.625454261</v>
+        <v>6538263</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4674,60 +4229,69 @@
           <t>Lerbo</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D-Kat-0609</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>fördelade på ca 8 dellokaler spridda i området, Området är anmält för avverkning</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Franzén</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Franzén, Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>106642991</v>
+        <v>106692527</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4752,40 +4316,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Berg Lerbo, knärot 350 m sso, Srm</t>
+          <t>Berg, S om, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584231.8416649629</v>
+        <v>584415</v>
       </c>
       <c r="R33" t="n">
-        <v>6538263.233435098</v>
+        <v>6538083</v>
       </c>
       <c r="S33" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4807,84 +4355,44 @@
           <t>Lerbo</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>D-Kat-0609</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>fördelade på ca 8 dellokaler spridda i området, Området är anmält för avverkning</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>106563685</v>
+        <v>122394474</v>
       </c>
       <c r="B34" t="n">
-        <v>95529</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4892,53 +4400,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221940</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mellanlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium zeilleri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Berg Lerbo, Srm</t>
+          <t>Berg, Berg, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584317.7396690836</v>
+        <v>584257</v>
       </c>
       <c r="R34" t="n">
-        <v>6538139.281049043</v>
+        <v>6538303</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4962,27 +4462,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Misstänkt lik den rödlistade mellanlummern</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4991,86 +4486,77 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>106692527</v>
+        <v>99110942</v>
       </c>
       <c r="B35" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Berg, S om, Srm</t>
+          <t>Sund Katrineborg, Katrineholm, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584415.059095733</v>
+        <v>584360</v>
       </c>
       <c r="R35" t="n">
-        <v>6538083.655209726</v>
+        <v>6538112</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5094,22 +4580,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5124,65 +4610,77 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Dan Åman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>106692515</v>
+        <v>106564025</v>
       </c>
       <c r="B36" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Berg, S om, Srm</t>
+          <t>Berg Lerbo 420 m s, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584400.1057739656</v>
+        <v>584357</v>
       </c>
       <c r="R36" t="n">
-        <v>6538082.295315696</v>
+        <v>6538121</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5212,100 +4710,101 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>106692476</v>
+        <v>106563685</v>
       </c>
       <c r="B37" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4189</v>
+        <v>221940</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Mellanlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Lycopodium zeilleri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Rouy) Greuter &amp; Burdet</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Berg, S om, Srm</t>
+          <t>Berg Lerbo, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584352.2377899707</v>
+        <v>584317</v>
       </c>
       <c r="R37" t="n">
-        <v>6538074.024049722</v>
+        <v>6538140</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5335,24 +4834,14 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ett fjolårsex under gammal gran. Området är avverkningsanmält.</t>
+          <t>Misstänkt lik den rödlistade mellanlummern</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5361,79 +4850,81 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Karlsson, Bo Törnquist, Monika Gustafsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122394474</v>
+        <v>106627405</v>
       </c>
       <c r="B38" t="n">
-        <v>98347</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97993</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221940</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mellanlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium zeilleri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Rouy) Greuter &amp; Burdet</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Berg, Berg, Srm</t>
+          <t>Berg, Lerbo, Biesta, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584257</v>
+        <v>584321</v>
       </c>
       <c r="R38" t="n">
-        <v>6538303</v>
+        <v>6538115</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5457,22 +4948,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5481,21 +4962,264 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>106627978</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97993</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221940</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mellanlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium zeilleri</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Rouy) Greuter &amp; Burdet</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lerbo Berg, 400 m SSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>584313</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6538144</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lerbo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-02-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-02-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Varav två skott tagna som belägg av Bo Karlsson. Tio skott med sporaxskaft med 3-6 sporax per skaft. Sporaxskaften utgår både från centralskottet och från sidogrenar. Smala ändgrenar, cirka 1,5 mm. Dorsalbladen nästan lika stora som lateralbladen i grenspetsarna, ventralbladen något kortare och smalare. Lateralbladens spetsar inböjda, med några få undantag. Jordskott 6-8 cm under yttre markskiktet. Hela beståndet inom ett begränsat område, som i övrigt endast hyser ett fåtal kärlväxter. Skogspartiet är anmält för avverkning.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Mossig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>99035745</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sund Katrineborg, Katrineholm, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>584330</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6538130</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lerbo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-03-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-03-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Dan Åman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Dan Åman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44206-2021 artfynd.xlsx
+++ b/artfynd/A 44206-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563513</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563582</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106692476</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563215</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106562883</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,6 +1633,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563629</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1717,6 +1762,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563772</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1834,6 +1884,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99035434</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1958,6 +2013,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563508</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2082,6 +2142,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563577</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2206,6 +2271,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563712</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2330,6 +2400,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563983</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2431,6 +2506,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106627332</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2531,6 +2611,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106692515</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2657,6 +2742,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563242</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2765,6 +2855,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17147551</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2880,6 +2975,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98155950</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2995,6 +3095,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156145</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3110,6 +3215,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156204</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3225,6 +3335,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156284</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3340,6 +3455,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98157785</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3450,6 +3570,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98158382</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3560,6 +3685,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98158490</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3675,6 +3805,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98158571</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3790,6 +3925,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98158635</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3908,6 +4048,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99035198</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4036,6 +4181,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563795</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4143,6 +4293,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106627216</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4283,6 +4438,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106642991</t>
         </is>
       </c>
     </row>
@@ -4386,6 +4546,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106692527</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4501,6 +4666,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122394474</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4619,6 +4789,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99110942</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4747,6 +4922,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106564025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4876,6 +5056,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106563685</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4978,6 +5163,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106627405</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5102,6 +5292,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106627978</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5220,8 +5415,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99035745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>